--- a/sheet-template/GAMEOVER_전체시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_전체시트_261012.xlsx
@@ -1154,7 +1154,11 @@
           <t>industry-1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>세션 제목 미정</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1226,7 +1230,11 @@
           <t>industry-2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>세션 제목 미정</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1362,7 +1370,11 @@
           <t>indie-1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>세션 제목 미정</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1434,7 +1446,11 @@
           <t>indie-2</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>세션 제목 미정</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1506,7 +1522,11 @@
           <t>indie-3</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>세션 제목 미정</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1578,7 +1598,11 @@
           <t>indie-4</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>세션 제목 미정</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">

--- a/sheet-template/GAMEOVER_전체시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_전체시트_261012.xlsx
@@ -1696,7 +1696,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>오전에 받은 참가지의 도장 세 개를 모으면 응모할 수 있습니다</t>
+          <t>모든 세션에 참석하신 분은 누구나 응모할 수 있습니다</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>됩니다. 세션은 35분, 쉬는 시간은 10분이라 중간에 드나드셔도 됩니다. 다만 럭키 드로우 응모에는 도장 세 개가 필요해 최소 세 세션은 들으셔야 합니다.</t>
+          <t>됩니다. 세션은 35분, 쉬는 시간은 10분이라 중간에 드나드셔도 됩니다. 다만 럭키 드로우는 모든 세션에 참석하신 분만 응모할 수 있습니다.</t>
         </is>
       </c>
     </row>

--- a/sheet-template/GAMEOVER_전체시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_전체시트_261012.xlsx
@@ -589,7 +589,11 @@
           <t>신청 주소</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSd0A2eNWlyCQG0KL_oU8xe7tlNwGzSye7eTCJSlkLt40ikBHg/viewform</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>구글 폼 주소. 비우면 신청 버튼이 '준비 중'으로 보입니다</t>
@@ -2083,12 +2087,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신청은 언제부터 하나요?</t>
+          <t>신청은 어떻게 하나요?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10월 초에 이 페이지에서 사전 신청을 받고 10월 24일 (토)에 마감합니다. 지금은 수요조사만 받고 있습니다.</t>
+          <t>이 페이지의 「참가 신청하기」 버튼으로 신청하실 수 있습니다. 마감은 10월 24일 (토)입니다.</t>
         </is>
       </c>
     </row>

--- a/sheet-template/GAMEOVER_전체시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_전체시트_261012.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>세션 제목 미정</t>
+          <t>AI 시대에서 살아남기</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>세션 제목 미정</t>
+          <t>AI를 사용한 게임 개발 사례와 실무 이야기</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>세션 제목 미정</t>
+          <t>실패를 퀘스트로 만들었습니다</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>세션 제목 미정</t>
+          <t>내가 게임을 다시 처음 만든다면</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>세션 제목 미정</t>
+          <t>게임잼에서 출시까지</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>세션 제목 미정</t>
+          <t>게임 불모지 울산에서 게임으로 살아남기</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>

--- a/sheet-template/GAMEOVER_전체시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_전체시트_261012.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동명대학교 게임 개발 동아리 연합 · UPTRAND × 기즈모</t>
+          <t>CHECKPOINT · 부울경 게임 개발 동아리 연합</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/sheet-template/GAMEOVER_전체시트_261012.xlsx
+++ b/sheet-template/GAMEOVER_전체시트_261012.xlsx
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1308,12 +1308,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1340,12 +1340,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
           <t>13:55</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1416,12 +1416,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1460,12 +1460,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
           <t>14:40</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1492,12 +1492,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1536,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
           <t>15:25</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
           <t>16:10</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1644,12 +1644,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1676,12 +1676,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>17:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1740,7 +1740,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
